--- a/data/processed/model_avg_scores.xlsx
+++ b/data/processed/model_avg_scores.xlsx
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8846564118455096</v>
+        <v>0.8846564074841942</v>
       </c>
       <c r="C4" t="n">
         <v>0.9427527189254761</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9137045762887815</v>
+        <v>0.9137045741081238</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.792786609835741</v>
+        <v>0.7927866083819691</v>
       </c>
       <c r="C8" t="n">
         <v>0.8883442878723145</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8405654612110882</v>
+        <v>0.8405654604842023</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5549715815520868</v>
+        <v>0.5549715800983149</v>
       </c>
       <c r="C9" t="n">
         <v>0.7221377491950989</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6385546570144048</v>
+        <v>0.638554656287519</v>
       </c>
     </row>
   </sheetData>
